--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_HAPOEL IBI TEL AVIV.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_HAPOEL IBI TEL AVIV.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA44"/>
+  <dimension ref="A1:BA42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,13 +671,13 @@
         <v>0.2239382239382239</v>
       </c>
       <c r="J2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>42</v>
@@ -752,13 +752,13 @@
         <v>1</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.5681818181818182</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9743589743589743</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.777777777777778</v>
+        <v>3</v>
       </c>
       <c r="AN2" t="n">
         <v>1.177777777777778</v>
@@ -801,13 +801,13 @@
         <v>0.2239382239382239</v>
       </c>
       <c r="J3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>0.75</v>
       </c>
       <c r="M3" t="n">
         <v>10.5</v>
@@ -882,13 +882,13 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.5681818181818182</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9743589743589743</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.777777777777778</v>
+        <v>3</v>
       </c>
       <c r="AN3" t="n">
         <v>1.177777777777778</v>
@@ -931,13 +931,13 @@
         <v>0.1781818181818182</v>
       </c>
       <c r="J4" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>40</v>
@@ -1012,13 +1012,13 @@
         <v>1.042372881355932</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.088888888888889</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.042553191489362</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.782608695652174</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
         <v>1.840909090909091</v>
@@ -1061,13 +1061,13 @@
         <v>0.1781818181818182</v>
       </c>
       <c r="J5" t="n">
-        <v>12.25</v>
+        <v>0.75</v>
       </c>
       <c r="K5" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>10.25</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>10</v>
@@ -1142,13 +1142,13 @@
         <v>1.042372881355932</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.088888888888889</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.042553191489362</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.782608695652174</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>1.840909090909091</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>34:17</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AO8" t="n">
@@ -1575,13 +1575,13 @@
         <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.083</v>
+        <v>0.197</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.031</v>
+        <v>0.074</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.063</v>
+        <v>0.148</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -1651,16 +1651,16 @@
         <v>56</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>17</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>207:50</t>
+          <t>98:10</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,13 +1740,13 @@
         <v>4.545</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.119</v>
+        <v>0.252</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.041</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="BA9" t="n">
         <v>0.156</v>
@@ -1816,16 +1816,16 @@
         <v>32</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>8</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>149:06</t>
+          <t>79:16</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1905,13 +1905,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.148</v>
+        <v>0.279</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.014</v>
+        <v>0.027</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.043</v>
+        <v>0.081</v>
       </c>
       <c r="BA10" t="n">
         <v>0.03</v>
@@ -1981,16 +1981,16 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>14</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>221:31</t>
+          <t>111:43</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,13 +2070,13 @@
         <v>8.167</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.107</v>
+        <v>0.212</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.082</v>
+        <v>0.163</v>
       </c>
       <c r="BA11" t="n">
         <v>0.092</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>00:19</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>21:47</t>
+          <t>01:47</t>
         </is>
       </c>
       <c r="AO13" t="n">
@@ -2479,13 +2479,13 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>6</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>134:58</t>
+          <t>65:20</t>
         </is>
       </c>
       <c r="AO14" t="n">
@@ -2565,13 +2565,13 @@
         <v>7</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.055</v>
+        <v>0.115</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.024</v>
+        <v>0.049</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.127</v>
+        <v>0.263</v>
       </c>
       <c r="BA14" t="n">
         <v>0.019</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>94:25</t>
+          <t>34:25</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,13 +2730,13 @@
         <v>7</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.049</v>
+        <v>0.135</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.023</v>
+        <v>0.062</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.023</v>
+        <v>0.062</v>
       </c>
       <c r="BA15" t="n">
         <v>0</v>
@@ -2809,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>91:38</t>
+          <t>41:39</t>
         </is>
       </c>
       <c r="AO16" t="n">
@@ -2895,13 +2895,13 @@
         <v>4.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.051</v>
+        <v>0.113</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.023</v>
+        <v>0.052</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.023</v>
+        <v>0.052</v>
       </c>
       <c r="BA16" t="n">
         <v>0.018</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>80:38</t>
+          <t>30:50</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -3060,13 +3060,13 @@
         <v>2.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.046</v>
+        <v>0.121</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.04</v>
+        <v>0.104</v>
       </c>
       <c r="BA17" t="n">
         <v>0</v>
@@ -3136,16 +3136,16 @@
         <v>73</v>
       </c>
       <c r="U18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>16</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>168:25</t>
+          <t>108:25</t>
         </is>
       </c>
       <c r="AO18" t="n">
@@ -3225,13 +3225,13 @@
         <v>6.444</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.155</v>
+        <v>0.24</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.026</v>
+        <v>0.04</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.108</v>
+        <v>0.168</v>
       </c>
       <c r="BA18" t="n">
         <v>0.179</v>
@@ -3301,7 +3301,7 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>173:58</t>
+          <t>84:26</t>
         </is>
       </c>
       <c r="AO19" t="n">
@@ -3390,13 +3390,13 @@
         <v>20</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.055</v>
+        <v>0.112</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.019</v>
+        <v>0.038</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.025</v>
+        <v>0.051</v>
       </c>
       <c r="BA19" t="n">
         <v>0.008999999999999999</v>
@@ -3466,16 +3466,16 @@
         <v>102</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>30</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>198:10</t>
+          <t>118:09</t>
         </is>
       </c>
       <c r="AO20" t="n">
@@ -3555,13 +3555,13 @@
         <v>16.333</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.142</v>
+        <v>0.239</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.054</v>
+        <v>0.091</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.108</v>
+        <v>0.182</v>
       </c>
       <c r="BA20" t="n">
         <v>0.012</v>
@@ -3634,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AO21" t="n">
@@ -3726,7 +3726,7 @@
         <v>0.097</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.194</v>
+        <v>0.195</v>
       </c>
       <c r="BA21" t="n">
         <v>0.027</v>
@@ -3900,65 +3900,65 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="T23" t="n">
-        <v>9</v>
+        <v>374</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -3967,96 +3967,96 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>0.396</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.294</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>800:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>1</v>
+        <v>337</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>0.494</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>0.224</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.178</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>5.756</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>6.933</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
       <c r="BA23" t="n">
         <v>0</v>
@@ -4065,44 +4065,44 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="D24" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E24" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="H24" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I24" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="J24" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="K24" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="L24" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M24" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N24" t="n">
         <v>30</v>
@@ -4111,76 +4111,76 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q24" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R24" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="S24" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="T24" t="n">
-        <v>374</v>
+        <v>429</v>
       </c>
       <c r="U24" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>103</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>31</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>78</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK24" t="n">
         <v>38</v>
       </c>
-      <c r="W24" t="n">
-        <v>48</v>
-      </c>
-      <c r="X24" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>119</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>91</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>28</v>
-      </c>
       <c r="AL24" t="n">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.337</v>
+        <v>0.333</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
@@ -4188,40 +4188,40 @@
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>337</v>
+        <v>346.72</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.494</v>
+        <v>0.536</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.538</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.992</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.134</v>
+        <v>0.127</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.224</v>
+        <v>0.178</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.178</v>
+        <v>1.841</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.756</v>
+        <v>6.25</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.933</v>
+        <v>8.090999999999999</v>
       </c>
       <c r="AX24" t="n">
         <v>0.2</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.052</v>
+        <v>0.063</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.137</v>
+        <v>0.148</v>
       </c>
       <c r="BA24" t="n">
         <v>0</v>
@@ -4230,895 +4230,895 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4</v>
-      </c>
-      <c r="C25" t="n">
-        <v>344</v>
-      </c>
-      <c r="D25" t="n">
-        <v>86</v>
-      </c>
-      <c r="E25" t="n">
-        <v>157</v>
-      </c>
-      <c r="F25" t="n">
-        <v>41</v>
-      </c>
-      <c r="G25" t="n">
-        <v>118</v>
-      </c>
-      <c r="H25" t="n">
-        <v>49</v>
-      </c>
-      <c r="I25" t="n">
-        <v>63</v>
-      </c>
-      <c r="J25" t="n">
-        <v>81</v>
-      </c>
-      <c r="K25" t="n">
-        <v>110</v>
-      </c>
-      <c r="L25" t="n">
-        <v>47</v>
-      </c>
-      <c r="M25" t="n">
-        <v>27</v>
-      </c>
-      <c r="N25" t="n">
-        <v>30</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>40</v>
-      </c>
-      <c r="R25" t="n">
-        <v>75</v>
-      </c>
-      <c r="S25" t="n">
-        <v>71</v>
-      </c>
-      <c r="T25" t="n">
-        <v>429</v>
-      </c>
-      <c r="U25" t="n">
-        <v>49</v>
-      </c>
-      <c r="V25" t="n">
-        <v>49</v>
-      </c>
-      <c r="W25" t="n">
-        <v>41</v>
-      </c>
-      <c r="X25" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>103</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>122</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>31</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>78</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0.397</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>114</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>800:00</t>
-        </is>
-      </c>
-      <c r="AO25" t="n">
-        <v>346.72</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1.841</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>8.090999999999999</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr"/>
-      <c r="AX26" t="inlineStr"/>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr"/>
-      <c r="BA26" t="inlineStr"/>
+          <t>#0 J. MOTLEY (Per Game)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>03:37</t>
+        </is>
+      </c>
+      <c r="AO26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#0 J. MOTLEY (Per Game)</t>
+          <t>#1 C. JONES (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="n">
+        <v>13</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" t="n">
         <v>0.5</v>
       </c>
-      <c r="D27" t="n">
+      <c r="M27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T27" t="n">
+        <v>56</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AE27" t="n">
         <v>0.25</v>
       </c>
-      <c r="E27" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="AF27" t="n">
         <v>0.5</v>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="AG27" t="n">
         <v>0.5</v>
       </c>
-      <c r="L27" t="n">
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
         <v>0.25</v>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ27" t="n">
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.417</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>24:32</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>1.5</v>
+        <v>13.04</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.2</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.2</v>
+        <v>0.632</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.333</v>
+        <v>0.997</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.167</v>
+        <v>0.211</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>0.371</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.364</v>
       </c>
       <c r="AV27" t="n">
-        <v>5</v>
+        <v>3.182</v>
       </c>
       <c r="AW27" t="n">
-        <v>5</v>
+        <v>4.545</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.083</v>
+        <v>0.252</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.031</v>
+        <v>0.022</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.063</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#1 C. JONES (Per Game)</t>
+          <t>#2 A. BLAKENEY (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>13.667</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>1.667</v>
       </c>
       <c r="E28" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>1.25</v>
+        <v>2.667</v>
       </c>
       <c r="G28" t="n">
-        <v>3.25</v>
+        <v>7.667</v>
       </c>
       <c r="H28" t="n">
-        <v>3.25</v>
+        <v>2.333</v>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>2.667</v>
       </c>
       <c r="J28" t="n">
-        <v>3.75</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>2</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="M28" t="n">
-        <v>0.75</v>
+        <v>0.333</v>
       </c>
       <c r="N28" t="n">
-        <v>0.5</v>
+        <v>1.333</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.75</v>
+        <v>1.667</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.75</v>
+        <v>1.667</v>
       </c>
       <c r="R28" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="U28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AD28" t="n">
-        <v>0.538</v>
+        <v>0.333</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.25</v>
+        <v>0.667</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.5</v>
+        <v>2.333</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
       <c r="AH28" t="n">
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.25</v>
+        <v>2.667</v>
       </c>
       <c r="AL28" t="n">
-        <v>3</v>
+        <v>7.333</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.417</v>
+        <v>0.364</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>51:57</t>
+          <t>26:25</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>13.04</v>
+        <v>15.507</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.447</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.632</v>
+        <v>0.494</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.997</v>
+        <v>0.881</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.211</v>
+        <v>0.107</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.371</v>
+        <v>0.184</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.364</v>
+        <v>0.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.182</v>
+        <v>7.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.545</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.119</v>
+        <v>0.279</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.01</v>
+        <v>0.027</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.041</v>
+        <v>0.081</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.156</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#2 A. BLAKENEY (Per Game)</t>
+          <t>#3 E. BRYANT (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>13.667</v>
+        <v>10.5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.667</v>
+        <v>2.75</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="F29" t="n">
-        <v>2.667</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>7.667</v>
+        <v>3.75</v>
       </c>
       <c r="H29" t="n">
-        <v>2.333</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>2.667</v>
+        <v>2.25</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>4.25</v>
       </c>
       <c r="L29" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="M29" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="N29" t="n">
-        <v>1.333</v>
+        <v>0.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.667</v>
+        <v>1.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.667</v>
+        <v>1.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>3.333</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.667</v>
+        <v>3.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.889</v>
+        <v>0.875</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="AC29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.667</v>
+        <v>0.25</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.333</v>
+        <v>0.25</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.286</v>
+        <v>1</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.667</v>
+        <v>0.75</v>
       </c>
       <c r="AL29" t="n">
-        <v>7.333</v>
+        <v>3.5</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.364</v>
+        <v>0.214</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>49:42</t>
+          <t>27:55</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>15.507</v>
+        <v>12.49</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.447</v>
+        <v>0.425</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.494</v>
+        <v>0.478</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.881</v>
+        <v>0.841</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.107</v>
+        <v>0.12</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.184</v>
+        <v>0.2</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>7.6</v>
+        <v>6.667</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.167</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.148</v>
+        <v>0.212</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.043</v>
+        <v>0.163</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.042</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#3 E. BRYANT (Per Game)</t>
+          <t>#9 G. PALATIN (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>50</v>
+        <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>55:22</t>
+          <t>00:19</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>12.49</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.425</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.478</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.841</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>6.667</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>8.167</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.082</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#9 G. PALATIN (Per Game)</t>
+          <t>#10 B. TIMOR (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -5166,13 +5166,13 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>00:53</t>
         </is>
       </c>
       <c r="AO31" t="n">
@@ -5279,92 +5279,92 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#10 B. TIMOR (Per Game)</t>
+          <t>#15 K. EDWARDS (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T32" t="n">
+        <v>35</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z32" t="n">
         <v>2</v>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -5373,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -5382,109 +5382,109 @@
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AJ32" t="n">
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.142</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#15 K. EDWARDS (Per Game)</t>
+          <t>#17 C. MALCOLM (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
         <v>4.5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="E33" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="H33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K33" t="n">
-        <v>4</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.75</v>
-      </c>
       <c r="N33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5499,46 +5499,46 @@
         <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="T33" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -5547,109 +5547,109 @@
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>33:44</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>3.94</v>
+        <v>4.88</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.625</v>
+        <v>0.429</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.654</v>
+        <v>0.514</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.142</v>
+        <v>0.922</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.127</v>
+        <v>0.102</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.25</v>
+        <v>0.429</v>
       </c>
       <c r="AU33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW33" t="n">
         <v>7</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.055</v>
+        <v>0.135</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.024</v>
+        <v>0.062</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.127</v>
+        <v>0.062</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#17 C. MALCOLM (Per Game)</t>
+          <t>#20 L. RANDOLPH (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>4.5</v>
+        <v>1.25</v>
       </c>
       <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
         <v>1.5</v>
       </c>
-      <c r="E34" t="n">
-        <v>3</v>
-      </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H34" t="n">
         <v>0.5</v>
       </c>
-      <c r="H34" t="n">
-        <v>1.5</v>
-      </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5658,46 +5658,46 @@
         <v>0.5</v>
       </c>
       <c r="Q34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
         <v>0.5</v>
       </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>11</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z34" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AA34" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -5709,112 +5709,112 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
         <v>0</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>47:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>4.88</v>
+        <v>2.47</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.429</v>
+        <v>0.214</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.514</v>
+        <v>0.317</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.922</v>
+        <v>0.506</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.102</v>
+        <v>0.202</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.429</v>
+        <v>0.286</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV34" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.049</v>
+        <v>0.113</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.023</v>
+        <v>0.052</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.023</v>
+        <v>0.052</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#20 L. RANDOLPH (Per Game)</t>
+          <t>#21 T. ODIASE (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E35" t="n">
         <v>1.25</v>
       </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.5</v>
-      </c>
       <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
         <v>0.25</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.5</v>
       </c>
       <c r="I35" t="n">
         <v>0.5</v>
       </c>
       <c r="J35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5823,64 +5823,64 @@
         <v>0.5</v>
       </c>
       <c r="Q35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
         <v>0.25</v>
       </c>
-      <c r="R35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="Z35" t="n">
         <v>0.25</v>
       </c>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AA35" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
         <v>0</v>
@@ -5893,306 +5893,306 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>22:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>2.47</v>
+        <v>1.97</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.317</v>
+        <v>0.255</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.506</v>
+        <v>0.381</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.202</v>
+        <v>0.254</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.286</v>
+        <v>0.2</v>
       </c>
       <c r="AU35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.051</v>
+        <v>0.121</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.023</v>
+        <v>0.104</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#21 T. ODIASE (Per Game)</t>
+          <t>#22 V. MICIC (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>0.75</v>
+        <v>12.5</v>
       </c>
       <c r="D36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="T36" t="n">
+        <v>73</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
         <v>0.25</v>
       </c>
-      <c r="E36" t="n">
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
         <v>1.25</v>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I36" t="n">
+      <c r="AL36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>27:06</t>
+        </is>
+      </c>
+      <c r="AO36" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="AP36" t="n">
         <v>0.5</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>20:09</t>
-        </is>
-      </c>
-      <c r="AO36" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0.2</v>
-      </c>
       <c r="AQ36" t="n">
-        <v>0.255</v>
+        <v>0.545</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.381</v>
+        <v>0.912</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.254</v>
+        <v>0.164</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>1.889</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.5</v>
+        <v>4.556</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.5</v>
+        <v>6.444</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.046</v>
+        <v>0.24</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.04</v>
+        <v>0.168</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#22 V. MICIC (Per Game)</t>
+          <t>#24 I. WAINRIGHT (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="D37" t="n">
-        <v>3.25</v>
+        <v>0.25</v>
       </c>
       <c r="E37" t="n">
-        <v>6.25</v>
+        <v>1.25</v>
       </c>
       <c r="F37" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="H37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>4.25</v>
+        <v>0.25</v>
       </c>
       <c r="K37" t="n">
-        <v>4.25</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="N37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>0.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="R37" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="S37" t="n">
-        <v>5.75</v>
+        <v>0.25</v>
       </c>
       <c r="T37" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="X37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC37" t="n">
         <v>0.75</v>
       </c>
-      <c r="Y37" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AD37" t="n">
-        <v>0.462</v>
+        <v>0.333</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6207,247 +6207,247 @@
         <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ37" t="n">
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AL37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.312</v>
+        <v>0.333</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>42:06</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>13.71</v>
+        <v>5</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.5</v>
+        <v>0.368</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.545</v>
+        <v>0.368</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.912</v>
+        <v>0.7</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.164</v>
+        <v>0.05</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.889</v>
+        <v>1</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.556</v>
+        <v>19</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.444</v>
+        <v>20</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.155</v>
+        <v>0.112</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.026</v>
+        <v>0.038</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.108</v>
+        <v>0.051</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.179</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#24 I. WAINRIGHT (Per Game)</t>
+          <t>#25 D. OTURU (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>3.5</v>
+        <v>19</v>
       </c>
       <c r="D38" t="n">
-        <v>0.25</v>
+        <v>8.25</v>
       </c>
       <c r="E38" t="n">
-        <v>1.25</v>
+        <v>12</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="J38" t="n">
         <v>0.25</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
         <v>0.75</v>
       </c>
-      <c r="M38" t="n">
+      <c r="Q38" t="n">
         <v>0.75</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="n">
+        <v>102</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AE38" t="n">
         <v>0.25</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
       </c>
       <c r="AF38" t="n">
         <v>0.25</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>29:32</t>
+        </is>
+      </c>
+      <c r="AO38" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="AU38" t="n">
         <v>0.333</v>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>43:29</t>
-        </is>
-      </c>
-      <c r="AO38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>1</v>
-      </c>
       <c r="AV38" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AW38" t="n">
-        <v>20</v>
+        <v>16.333</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.055</v>
+        <v>0.239</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.019</v>
+        <v>0.091</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.025</v>
+        <v>0.182</v>
       </c>
       <c r="BA38" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#25 D. OTURU (Per Game)</t>
+          <t>#26 Y. MADAR (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>19</v>
+        <v>0.667</v>
       </c>
       <c r="D39" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>12</v>
+        <v>0.667</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -6456,163 +6456,163 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2.5</v>
+        <v>0.667</v>
       </c>
       <c r="I39" t="n">
-        <v>4.75</v>
+        <v>0.667</v>
       </c>
       <c r="J39" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="T39" t="n">
+        <v>7</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="AO39" t="n">
+        <v>1.293</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW39" t="n">
         <v>5</v>
       </c>
-      <c r="L39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S39" t="n">
-        <v>4</v>
-      </c>
-      <c r="T39" t="n">
-        <v>102</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>49:32</t>
-        </is>
-      </c>
-      <c r="AO39" t="n">
-        <v>14.84</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>16.333</v>
-      </c>
       <c r="AX39" t="n">
-        <v>0.142</v>
+        <v>0.167</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.054</v>
+        <v>0.097</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.108</v>
+        <v>0.195</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.012</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#26 Y. MADAR (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -6621,22 +6621,22 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.667</v>
+        <v>0.75</v>
       </c>
       <c r="L40" t="n">
-        <v>0.333</v>
+        <v>1.75</v>
       </c>
       <c r="M40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -6645,25 +6645,25 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -6672,19 +6672,19 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -6718,209 +6718,209 @@
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>03:41</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>1.293</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
         <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.347</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.515</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.258</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>78.5</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>20.75</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>42.25</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>13.25</v>
       </c>
       <c r="K41" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="L41" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="N41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="S41" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="T41" t="n">
+        <v>374</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
         <v>0.75</v>
       </c>
-      <c r="L41" t="n">
+      <c r="X41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI41" t="n">
         <v>1.75</v>
       </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>20.75</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>84.25</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>0.494</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>0.224</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>1.178</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>5.756</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>6.933</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
       <c r="BA41" t="n">
         <v>0</v>
@@ -6929,68 +6929,68 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>39.25</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>29.5</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>12.25</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="T42" t="n">
-        <v>9</v>
+        <v>429</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -7002,422 +7002,92 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>25.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>30.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>0.844</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>0.397</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>28.5</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>0.25</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>0.536</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>0.992</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>0.178</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>1.841</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>8.090999999999999</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>0.206</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>4</v>
-      </c>
-      <c r="C43" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="D43" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="E43" t="n">
-        <v>42.25</v>
-      </c>
-      <c r="F43" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G43" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I43" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="J43" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="K43" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="L43" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="M43" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="N43" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="R43" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="S43" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="T43" t="n">
-        <v>374</v>
-      </c>
-      <c r="U43" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="V43" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W43" t="n">
-        <v>12</v>
-      </c>
-      <c r="X43" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO43" t="n">
-        <v>84.25</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0.9320000000000001</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>1.178</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>5.756</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>6.933</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>4</v>
-      </c>
-      <c r="C44" t="n">
-        <v>86</v>
-      </c>
-      <c r="D44" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="E44" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="F44" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="G44" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="H44" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="I44" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="J44" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="K44" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="L44" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="N44" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>10</v>
-      </c>
-      <c r="R44" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="S44" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="T44" t="n">
-        <v>429</v>
-      </c>
-      <c r="U44" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="V44" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="W44" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="X44" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0.397</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO44" t="n">
-        <v>86.68000000000001</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>1.841</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>8.090999999999999</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="BA44" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_HAPOEL IBI TEL AVIV.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_HAPOEL IBI TEL AVIV.xlsx
@@ -671,13 +671,13 @@
         <v>0.2239382239382239</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="M2" t="n">
         <v>42</v>
@@ -752,13 +752,13 @@
         <v>1</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>3</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AN2" t="n">
         <v>1.177777777777778</v>
@@ -801,13 +801,13 @@
         <v>0.2239382239382239</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="L3" t="n">
-        <v>0.75</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>10.5</v>
@@ -882,13 +882,13 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>3</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AN3" t="n">
         <v>1.177777777777778</v>
@@ -931,13 +931,13 @@
         <v>0.1781818181818182</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M4" t="n">
         <v>40</v>
@@ -1012,13 +1012,13 @@
         <v>1.042372881355932</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.06666666666666667</v>
+        <v>1.155555555555555</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.042553191489362</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AN4" t="n">
         <v>1.840909090909091</v>
@@ -1061,13 +1061,13 @@
         <v>0.1781818181818182</v>
       </c>
       <c r="J5" t="n">
-        <v>0.75</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>12.25</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="M5" t="n">
         <v>10</v>
@@ -1142,13 +1142,13 @@
         <v>1.042372881355932</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.06666666666666667</v>
+        <v>1.155555555555555</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.042553191489362</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AN5" t="n">
         <v>1.840909090909091</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1651,16 +1651,16 @@
         <v>56</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="n">
         <v>17</v>
@@ -1816,16 +1816,16 @@
         <v>32</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="n">
         <v>8</v>
@@ -1981,16 +1981,16 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="n">
         <v>14</v>
@@ -2479,13 +2479,13 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>6</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2809,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -3136,16 +3136,16 @@
         <v>73</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
         <v>16</v>
@@ -3301,7 +3301,7 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3466,16 +3466,16 @@
         <v>102</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
         <v>30</v>
@@ -3634,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -3961,16 +3961,16 @@
         <v>374</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="W23" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Y23" t="n">
         <v>100</v>
@@ -4126,16 +4126,16 @@
         <v>429</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y24" t="n">
         <v>103</v>
@@ -4353,7 +4353,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4515,16 +4515,16 @@
         <v>56</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y27" t="n">
         <v>4.25</v>
@@ -4680,16 +4680,16 @@
         <v>32</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.333</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="Y28" t="n">
         <v>2.667</v>
@@ -4845,16 +4845,16 @@
         <v>50</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y29" t="n">
         <v>3.5</v>
@@ -5343,13 +5343,13 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Y32" t="n">
         <v>1.5</v>
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -5673,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -6000,16 +6000,16 @@
         <v>73</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="Y36" t="n">
         <v>4</v>
@@ -6165,7 +6165,7 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>102</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y38" t="n">
         <v>7.5</v>
@@ -6498,7 +6498,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -6825,16 +6825,16 @@
         <v>374</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="W41" t="n">
-        <v>0.75</v>
+        <v>12</v>
       </c>
       <c r="X41" t="n">
-        <v>0.25</v>
+        <v>6.75</v>
       </c>
       <c r="Y41" t="n">
         <v>25</v>
@@ -6990,16 +6990,16 @@
         <v>429</v>
       </c>
       <c r="U42" t="n">
-        <v>0.75</v>
+        <v>13</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>12.25</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y42" t="n">
         <v>25.75</v>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_HAPOEL IBI TEL AVIV.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_HAPOEL IBI TEL AVIV.xlsx
@@ -683,13 +683,13 @@
         <v>42</v>
       </c>
       <c r="N2" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="O2" t="n">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4594594594594595</v>
+        <v>0.2355212355212355</v>
       </c>
       <c r="Q2" t="n">
         <v>36</v>
@@ -713,22 +713,22 @@
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.02702702702702703</v>
+        <v>0.03088803088803089</v>
       </c>
       <c r="Z2" t="n">
         <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3204633204633205</v>
+        <v>0.3166023166023166</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8403361344537815</v>
+        <v>0.6885245901639344</v>
       </c>
       <c r="AD2" t="n">
         <v>0.3956043956043956</v>
@@ -737,13 +737,13 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3373493975903614</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.680672268907563</v>
+        <v>1.377049180327869</v>
       </c>
       <c r="AI2" t="n">
         <v>0.5882352941176471</v>
@@ -813,13 +813,13 @@
         <v>10.5</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="O3" t="n">
-        <v>29.75</v>
+        <v>15.25</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4594594594594595</v>
+        <v>0.2355212355212355</v>
       </c>
       <c r="Q3" t="n">
         <v>9</v>
@@ -843,22 +843,22 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02702702702702703</v>
+        <v>0.03088803088803089</v>
       </c>
       <c r="Z3" t="n">
         <v>7</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.75</v>
+        <v>20.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3204633204633205</v>
+        <v>0.3166023166023166</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8403361344537815</v>
+        <v>0.6885245901639344</v>
       </c>
       <c r="AD3" t="n">
         <v>0.3956043956043956</v>
@@ -867,13 +867,13 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3373493975903614</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.680672268907563</v>
+        <v>1.377049180327869</v>
       </c>
       <c r="AI3" t="n">
         <v>0.5882352941176471</v>
@@ -943,13 +943,13 @@
         <v>40</v>
       </c>
       <c r="N4" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="O4" t="n">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4436363636363637</v>
+        <v>0.2654545454545454</v>
       </c>
       <c r="Q4" t="n">
         <v>31</v>
@@ -970,25 +970,25 @@
         <v>0.02181818181818182</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01454545454545455</v>
+        <v>0.02545454545454546</v>
       </c>
       <c r="Z4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA4" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4145454545454546</v>
+        <v>0.4036363636363636</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8442622950819673</v>
+        <v>0.7397260273972602</v>
       </c>
       <c r="AD4" t="n">
         <v>0.3974358974358974</v>
@@ -997,13 +997,13 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.75</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG4" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.688524590163935</v>
+        <v>1.47945205479452</v>
       </c>
       <c r="AI4" t="n">
         <v>0.3333333333333333</v>
@@ -1073,13 +1073,13 @@
         <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>25.75</v>
+        <v>13.5</v>
       </c>
       <c r="O5" t="n">
-        <v>30.5</v>
+        <v>18.25</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4436363636363637</v>
+        <v>0.2654545454545454</v>
       </c>
       <c r="Q5" t="n">
         <v>7.75</v>
@@ -1100,25 +1100,25 @@
         <v>0.02181818181818182</v>
       </c>
       <c r="W5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01454545454545455</v>
+        <v>0.02545454545454546</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>28.5</v>
+        <v>27.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4145454545454546</v>
+        <v>0.4036363636363636</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8442622950819673</v>
+        <v>0.7397260273972602</v>
       </c>
       <c r="AD5" t="n">
         <v>0.3974358974358974</v>
@@ -1127,13 +1127,13 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.75</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG5" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.688524590163935</v>
+        <v>1.47945205479452</v>
       </c>
       <c r="AI5" t="n">
         <v>0.3333333333333333</v>
@@ -1663,13 +1663,13 @@
         <v>6</v>
       </c>
       <c r="Y9" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Z9" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.85</v>
+        <v>0.571</v>
       </c>
       <c r="AB9" t="n">
         <v>7</v>
@@ -1828,13 +1828,13 @@
         <v>4</v>
       </c>
       <c r="Y10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.889</v>
+        <v>0.5</v>
       </c>
       <c r="AB10" t="n">
         <v>2</v>
@@ -1993,13 +1993,13 @@
         <v>6</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Z11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="AB11" t="n">
         <v>4</v>
@@ -2488,13 +2488,13 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2653,13 +2653,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>3</v>
@@ -2818,13 +2818,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2983,13 +2983,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>1</v>
@@ -3148,13 +3148,13 @@
         <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Z18" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.8</v>
+        <v>0.636</v>
       </c>
       <c r="AB18" t="n">
         <v>6</v>
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
@@ -3352,10 +3352,10 @@
         <v>4</v>
       </c>
       <c r="AL19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.333</v>
+        <v>0.364</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
@@ -3478,13 +3478,13 @@
         <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Z20" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.857</v>
+        <v>0.8</v>
       </c>
       <c r="AB20" t="n">
         <v>12</v>
@@ -3643,13 +3643,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3973,13 +3973,13 @@
         <v>27</v>
       </c>
       <c r="Y23" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="Z23" t="n">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.84</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="AB23" t="n">
         <v>36</v>
@@ -4003,19 +4003,19 @@
         <v>2</v>
       </c>
       <c r="AI23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AK23" t="n">
         <v>28</v>
       </c>
       <c r="AL23" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.337</v>
+        <v>0.341</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
@@ -4138,13 +4138,13 @@
         <v>24</v>
       </c>
       <c r="Y24" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="Z24" t="n">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.844</v>
+        <v>0.74</v>
       </c>
       <c r="AB24" t="n">
         <v>31</v>
@@ -4165,19 +4165,19 @@
         <v>0.167</v>
       </c>
       <c r="AH24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.75</v>
+        <v>0.571</v>
       </c>
       <c r="AK24" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AL24" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AM24" t="n">
         <v>0.333</v>
@@ -4527,13 +4527,13 @@
         <v>1.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>4.25</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>1.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.85</v>
+        <v>0.571</v>
       </c>
       <c r="AB27" t="n">
         <v>1.75</v>
@@ -4692,13 +4692,13 @@
         <v>1.333</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.667</v>
+        <v>0.333</v>
       </c>
       <c r="Z28" t="n">
-        <v>3</v>
+        <v>0.667</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.889</v>
+        <v>0.5</v>
       </c>
       <c r="AB28" t="n">
         <v>0.667</v>
@@ -4857,13 +4857,13 @@
         <v>1.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="AB29" t="n">
         <v>1</v>
@@ -5352,13 +5352,13 @@
         <v>0.25</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -5517,13 +5517,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>1.5</v>
@@ -5682,13 +5682,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -5847,13 +5847,13 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0.25</v>
@@ -6012,13 +6012,13 @@
         <v>0.75</v>
       </c>
       <c r="Y36" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="Z36" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.8</v>
+        <v>0.636</v>
       </c>
       <c r="AB36" t="n">
         <v>1.5</v>
@@ -6207,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AJ37" t="n">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>1</v>
       </c>
       <c r="AL37" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.333</v>
+        <v>0.364</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6342,13 +6342,13 @@
         <v>1.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="Z38" t="n">
-        <v>8.75</v>
+        <v>6.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.857</v>
+        <v>0.8</v>
       </c>
       <c r="AB38" t="n">
         <v>3</v>
@@ -6507,13 +6507,13 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -6837,13 +6837,13 @@
         <v>6.75</v>
       </c>
       <c r="Y41" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>29.75</v>
+        <v>15.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.84</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="AB41" t="n">
         <v>9</v>
@@ -6867,19 +6867,19 @@
         <v>0.5</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AK41" t="n">
         <v>7</v>
       </c>
       <c r="AL41" t="n">
-        <v>20.75</v>
+        <v>20.5</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.337</v>
+        <v>0.341</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
@@ -7002,13 +7002,13 @@
         <v>6</v>
       </c>
       <c r="Y42" t="n">
-        <v>25.75</v>
+        <v>13.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>30.5</v>
+        <v>18.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.844</v>
+        <v>0.74</v>
       </c>
       <c r="AB42" t="n">
         <v>7.75</v>
@@ -7029,19 +7029,19 @@
         <v>0.167</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AI42" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.75</v>
+        <v>0.571</v>
       </c>
       <c r="AK42" t="n">
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="AL42" t="n">
-        <v>28.5</v>
+        <v>27.75</v>
       </c>
       <c r="AM42" t="n">
         <v>0.333</v>
